--- a/output/full_scan/batch_seq6_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-23.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6223</v>
+        <v>6168</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1062.661651129455</v>
+        <v>1204.449575631285</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6680</v>
+        <v>34.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,102 +552,102 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.01119293262961</v>
+        <v>72.07056103845443</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.28083497235681</v>
+        <v>21.70933717783277</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.8551207452043195</v>
+        <v>3.335384133986041</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>26.16081968663008</v>
+        <v>0.7271470872406741</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6288</v>
+        <v>6223</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1053.76371134358</v>
+        <v>1102.691554936583</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>24.25</v>
+        <v>6680</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>66.27963871117393</v>
+        <v>65.01119294474989</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.15350990936851</v>
+        <v>23.28083497235681</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3.476371134358034</v>
+        <v>0.8570640411316141</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.1976960959148643</v>
+        <v>26.16081968292093</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6204</v>
+        <v>6435</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>847.7169116478433</v>
+        <v>1053.735250390388</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>118.5</v>
+        <v>362</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>67.12271416592216</v>
+        <v>76.00041533214097</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>41.51306728210688</v>
+        <v>31.10469289607744</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.9496457213813532</v>
+        <v>3.515192991762631</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,48 +676,48 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.1262428823919545</v>
+        <v>5.960495026597073</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6168</v>
+        <v>6288</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>819.4495756312848</v>
+        <v>1038.76371134358</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>34.2</v>
+        <v>24.25</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>72.07056098717381</v>
+        <v>66.43049365804504</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.70933717989194</v>
+        <v>24.98991895014388</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.335384133986041</v>
+        <v>3.476371134358034</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7271470873334035</v>
+        <v>0.1972000239006539</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6435</v>
+        <v>6204</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>813.7352503903882</v>
+        <v>1007.716911647843</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>362</v>
+        <v>118.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.00041531834329</v>
+        <v>67.12271415128228</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>31.10469279661919</v>
+        <v>41.51306722614915</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.515192991762631</v>
+        <v>0.9496457213813532</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.960495027029793</v>
+        <v>0.1262428827010602</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6271</v>
+        <v>6182</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>774.7447679450141</v>
+        <v>987.632791895444</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>244.5</v>
+        <v>114.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.50617311721968</v>
+        <v>69.35314960235857</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.55624085312072</v>
+        <v>41.24540450977725</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.097242311410461</v>
+        <v>1.605869156830016</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.5949849658749713</v>
+        <v>1.755897621298109</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6209</v>
+        <v>6226</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>752.9400703535149</v>
+        <v>973.50717437892</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>90.3</v>
+        <v>13.75</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.17669604658714</v>
+        <v>59.53884797870094</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>40.10747356971887</v>
+        <v>14.12223230962296</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6128575439067157</v>
+        <v>2.319899499963972</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4681520234611858</v>
+        <v>0.0154630577599836</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6182</v>
+        <v>6259</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>747.6327918954441</v>
+        <v>964.1726685216788</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>114.5</v>
+        <v>36.15</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,29 +923,29 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>69.35314959153811</v>
+        <v>67.35636811600386</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>41.24540442619222</v>
+        <v>50.44828846273352</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.605869156830016</v>
+        <v>1.517266852167893</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.755897621442342</v>
+        <v>0.919053496212168</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>734.7168042329262</v>
+        <v>944.7168042329262</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1735</v>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.83040334925077</v>
+        <v>58.83040335569941</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>31.35101196286911</v>
+        <v>31.35101203023186</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>0.9036095763219624</v>
@@ -994,11 +994,11 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>6.303669205351994</v>
+        <v>6.303669204527594</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>734</v>
+        <v>924</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>53</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.95452418075255</v>
+        <v>63.95452426425495</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.1711071550913</v>
+        <v>20.17110711377234</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>5.628642575340512</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.3954873799338552</v>
+        <v>0.3954873797896118</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6196</v>
+        <v>6472</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>731.3071636781946</v>
+        <v>923.1024649755324</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>541</v>
+        <v>439.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.10144765259622</v>
+        <v>67.31062187561324</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>40.29595940162458</v>
+        <v>25.44759967998639</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5494689136250137</v>
+        <v>1.452596430781017</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.8893484262263271</v>
+        <v>8.163329927554564</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6259</v>
+        <v>6243</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>724.1726685216789</v>
+        <v>884</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>36.15</v>
+        <v>41.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>67.35636810946994</v>
+        <v>74.27719751146836</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>50.44828840038298</v>
+        <v>26.21149082810044</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.517266852167893</v>
+        <v>8.655359989931787</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.9190534962636824</v>
+        <v>0.9273314734898812</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6229</v>
+        <v>6446</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>713.2915548429628</v>
+        <v>879.1495919179298</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28.15</v>
+        <v>1095</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.7833326459109</v>
+        <v>76.55398512416174</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.55627375210276</v>
+        <v>42.79321225841569</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.559425117681674</v>
+        <v>0.7321357004192983</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,11 +1206,11 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.1207393971159434</v>
+        <v>8.284803265472263</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>705.4328633425055</v>
+        <v>875.4328633425055</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>156.5</v>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>71.21692075957424</v>
+        <v>71.21692075345557</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>62.94448218667007</v>
+        <v>62.94448225738858</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.7091313702086749</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.166589959193432</v>
+        <v>1.166589959090402</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6175</v>
+        <v>6229</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>698.1403983740238</v>
+        <v>868.2915548429628</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>110.5</v>
+        <v>28.15</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.02184687186635</v>
+        <v>58.78333261222711</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41.04333779231444</v>
+        <v>14.55627397599427</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9638429209360284</v>
+        <v>1.559425117681674</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0123002636728344</v>
+        <v>0.1207393973735149</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6465</v>
+        <v>6209</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>694.24318013476</v>
+        <v>867.9400703535149</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>68.5</v>
+        <v>90.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>66.32092690867171</v>
+        <v>57.17669605932152</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.50244051477548</v>
+        <v>40.10747348292322</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8175746270572977</v>
+        <v>0.6128575439067157</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.524835440241871</v>
+        <v>0.4681520234199823</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6243</v>
+        <v>6270</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>倍微</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>694</v>
+        <v>852.8883969231971</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>41.5</v>
+        <v>38.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>74.27719746695715</v>
+        <v>69.17323405535021</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.21149082902195</v>
+        <v>48.02399574943221</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8.655359989931787</v>
+        <v>1.902429317550964</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9273314733044324</v>
+        <v>0.343825024495521</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6270</v>
+        <v>6208</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>倍微</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>692.8883969231971</v>
+        <v>848.7884297245796</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>38.3</v>
+        <v>100.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>69.17323401104612</v>
+        <v>58.49103416429415</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>48.02399565201905</v>
+        <v>24.82111107920851</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.902429317550964</v>
+        <v>2.003630937058738</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3438250246191607</v>
+        <v>1.340250150168457</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6226</v>
+        <v>6207</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>683.5071743789201</v>
+        <v>836.9765480327021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13.75</v>
+        <v>155.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.5388479942609</v>
+        <v>66.14291041310996</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>14.12223231992664</v>
+        <v>66.07938630975907</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.319899499963972</v>
+        <v>0.6689980679076829</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.0154630577599836</v>
+        <v>1.26621713833185</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6446</v>
+        <v>6257</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>679.1495919179298</v>
+        <v>830.6330525778858</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1095</v>
+        <v>237</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>76.55398508818226</v>
+        <v>60.61571570681458</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>42.79321225841569</v>
+        <v>27.03994082969067</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7321357004192983</v>
+        <v>1.246324066079572</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>8.284803266914707</v>
+        <v>1.230840266780997</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6202</v>
+        <v>6462</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>674.4680349895386</v>
+        <v>820.0984343620695</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>122</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>65.46683033995858</v>
+        <v>52.63371844797517</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24.53724760891064</v>
+        <v>20.57511282958013</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3.966663222543006</v>
+        <v>1.891987729112314</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.67544405310167</v>
+        <v>0.6183368035422574</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6472</v>
+        <v>6411</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>673.1024649755321</v>
+        <v>806.2962863612905</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>439.5</v>
+        <v>104.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>67.31062182954666</v>
+        <v>58.28608389359109</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>25.44759963227072</v>
+        <v>31.42103563782786</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.452596430781017</v>
+        <v>1.447617060738621</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>8.163329928172711</v>
+        <v>0.6095675985094355</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6257</v>
+        <v>6217</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>670.6330525778858</v>
+        <v>804.0209569408369</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>60.61571570505255</v>
+        <v>54.08010177508756</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.03994085066243</v>
+        <v>15.00072170421951</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.246324066079572</v>
+        <v>2.994780047168842</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.230840266760371</v>
+        <v>1.034412819869716</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6208</v>
+        <v>6202</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>668.7884297245796</v>
+        <v>794.4680349895386</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>100.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.49103417233775</v>
+        <v>65.46683037534564</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.82111116291038</v>
+        <v>24.53724763886504</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.003630937058738</v>
+        <v>3.966663222543006</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.340250150044819</v>
+        <v>1.675444052895609</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6189</v>
+        <v>6213</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>660.9051966641612</v>
+        <v>787.9218968583538</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>53.7</v>
+        <v>281</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,49 +1824,49 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>53.32762433940941</v>
+        <v>55.09577194025904</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.32026264827954</v>
+        <v>14.6668905782678</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6018435353195236</v>
+        <v>1.661385295588076</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.1164454336792653</v>
+        <v>2.899469774391896</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6409</v>
+        <v>6271</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>660.597191522521</v>
+        <v>784.7447679450141</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>912</v>
+        <v>244.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.92511589498072</v>
+        <v>55.50617313132813</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.9970225552358</v>
+        <v>26.55624086242028</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3840739684040324</v>
+        <v>2.097242311410461</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,11 +1895,11 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>7.178755859749572</v>
+        <v>-0.5949849662870772</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>655.3961698539766</v>
+        <v>770.3961698539766</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>344</v>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.47819837029141</v>
+        <v>56.47819838389565</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>32.40096450915648</v>
+        <v>32.40096467067264</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.19660646855614</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-1.93569002655336</v>
+        <v>-1.935690027171585</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6213</v>
+        <v>6269</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>647.9218968583538</v>
+        <v>768.562460054737</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>281</v>
+        <v>83.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.09577192994316</v>
+        <v>65.36561406506013</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.66689050388388</v>
+        <v>31.33487043944347</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.661385295588076</v>
+        <v>2.205892154455798</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.899469774597926</v>
+        <v>1.617729176098437</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6415</v>
+        <v>6220</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>640.4507561290782</v>
+        <v>760.8514658912958</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>645</v>
+        <v>39.35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>62.36423452785902</v>
+        <v>69.63298162438247</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>28.49962327167075</v>
+        <v>56.43768568774158</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.396735254819737</v>
+        <v>1.18514658912958</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6.022896920565458</v>
+        <v>0.5571797758253385</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6462</v>
+        <v>6419</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>640.0984343620695</v>
+        <v>752.1197568825124</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.63371836984437</v>
+        <v>57.30110471243513</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>20.5751128430273</v>
+        <v>14.91359431091318</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.891987729112314</v>
+        <v>1.124326845931293</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6183368043046764</v>
+        <v>1.149886610634919</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6265</v>
+        <v>6218</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>631.6666112741951</v>
+        <v>744.0590255961216</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>56.6</v>
+        <v>40.1</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>54.25110635141239</v>
+        <v>60.44878617707109</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>33.66959295408428</v>
+        <v>13.63133250059304</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.6726380212536575</v>
+        <v>3.030653728282124</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.5020812413008597</v>
+        <v>0.3492276912845072</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6411</v>
+        <v>6175</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>626.2962863612905</v>
+        <v>738.1403983740238</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>104.5</v>
+        <v>110.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>58.28608387346784</v>
+        <v>62.02184688544337</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.42103560693774</v>
+        <v>41.04333773590291</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.447617060738621</v>
+        <v>0.9638429209360284</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.609567598653677</v>
+        <v>0.0123002635698092</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6432</v>
+        <v>6465</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>625.6361942586999</v>
+        <v>734.24318013476</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>74</v>
+        <v>68.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.91384001563535</v>
+        <v>66.32092691551114</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>44.51452646434573</v>
+        <v>31.50244039407481</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6247958882296536</v>
+        <v>0.8175746270572977</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1134937477838953</v>
+        <v>1.524835440277181</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6292</v>
+        <v>6196</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>624.1703325088821</v>
+        <v>731.3071636781946</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>62.2</v>
+        <v>541</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.74453443688332</v>
+        <v>60.10144766135151</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>34.6964207585125</v>
+        <v>40.29595940457651</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4579125102103993</v>
+        <v>0.5494689136250137</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0412314877429635</v>
+        <v>-0.8893484263293487</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6217</v>
+        <v>6197</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>624.0209569408369</v>
+        <v>723.4197472702926</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>273</v>
+        <v>350</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>54.08010177432831</v>
+        <v>70.24539501847507</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15.0007217345724</v>
+        <v>45.02084449035146</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.994780047168842</v>
+        <v>0.6033246267860827</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.034412819880026</v>
+        <v>-0.6364375053135802</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6184</v>
+        <v>6414</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>612.9410396282425</v>
+        <v>704.3581172971622</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>46.95</v>
+        <v>377.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>56.93505621295563</v>
+        <v>54.29563705665872</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30.82200485797515</v>
+        <v>26.46881448291248</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.649202276918144</v>
+        <v>0.8652151073951895</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0787766014917661</v>
+        <v>-2.651756796103999</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6197</v>
+        <v>6449</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>608.4197472702926</v>
+        <v>699.190154627678</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>70.24539497923298</v>
+        <v>53.89594540764394</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45.0208444638952</v>
+        <v>41.1732523798929</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6033246267860827</v>
+        <v>2.026814464991884</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.6364375045924042</v>
+        <v>-4.84565199630871</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6269</v>
+        <v>6265</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>598.562460054737</v>
+        <v>671.6666112741951</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>83.8</v>
+        <v>56.6</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>65.36561404444971</v>
+        <v>54.25110635394198</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>31.33487046852969</v>
+        <v>33.66959293768237</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>2.205892154455798</v>
+        <v>0.6726380212536575</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.617729176263285</v>
+        <v>-0.5020812413173443</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6207</v>
+        <v>6451</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>596.9765480327021</v>
+        <v>669.3077269766471</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>155.5</v>
+        <v>596</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>66.1429104009855</v>
+        <v>54.59197436205766</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>66.07938632713594</v>
+        <v>32.57181939262208</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6689980679076829</v>
+        <v>1.348472644230178</v>
       </c>
       <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.266217138507002</v>
+        <v>-5.917034068428197</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6414</v>
+        <v>6432</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>594.3581172971622</v>
+        <v>665.6361942586999</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>377.5</v>
+        <v>74</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>54.29563701944607</v>
+        <v>56.91384002326686</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>26.46881447298235</v>
+        <v>44.51452657047749</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8652151073951895</v>
+        <v>0.6247958882296536</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-2.651756795691856</v>
+        <v>0.113493747742682</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6449</v>
+        <v>6292</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>589.1901546276781</v>
+        <v>664.1703325088821</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>382</v>
+        <v>62.2</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.8959453987024</v>
+        <v>52.74453444203167</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>41.17325240114409</v>
+        <v>34.69642077107704</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.026814464991884</v>
+        <v>0.4579125102103993</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-4.845651995979033</v>
+        <v>-0.0412314878047812</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6220</v>
+        <v>6189</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>580.8514658912958</v>
+        <v>660.9051966641612</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39.35</v>
+        <v>53.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>69.63298162438247</v>
+        <v>53.32762439826514</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>56.43768563976799</v>
+        <v>28.32026268473712</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.18514658912958</v>
+        <v>0.6018435353195236</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.5571797758150343</v>
+        <v>-0.1164454338029008</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6218</v>
+        <v>6233</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>574.0590255961216</v>
+        <v>660.8980402930753</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>40.1</v>
+        <v>25.45</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>60.44878614091515</v>
+        <v>52.33280014069533</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.63133245014072</v>
+        <v>14.54342106444509</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3.030653728282124</v>
+        <v>1.538592441815885</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.34922769139784</v>
+        <v>0.225024493657181</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6419</v>
+        <v>6409</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>572.1197568825124</v>
+        <v>660.597191522521</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>155</v>
+        <v>912</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.30110471547594</v>
+        <v>59.9251159259783</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14.91359426880274</v>
+        <v>37.99702274834794</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.124326845931293</v>
+        <v>0.3840739684040324</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>1.149886610449456</v>
+        <v>7.178755867991825</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6284</v>
+        <v>6415</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>560.5976164891624</v>
+        <v>640.4507561290782</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>101</v>
+        <v>645</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.10621398897668</v>
+        <v>62.36423452785902</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>41.70986030903041</v>
+        <v>28.49962327167075</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4186394991199239</v>
+        <v>1.396735254819737</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.093514143650567</v>
+        <v>6.022896920565458</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6224</v>
+        <v>6282</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>556.3613328750757</v>
+        <v>636.481235438902</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>78.7</v>
+        <v>61.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>49.8291756443297</v>
+        <v>54.53359778343172</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.1055468628998</v>
+        <v>31.83310863553663</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4341864315230613</v>
+        <v>0.9585313499581424</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.7565261085217343</v>
+        <v>-0.3760736386550261</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6174</v>
+        <v>6184</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>553.3012113274491</v>
+        <v>612.9410396282425</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>48.95</v>
+        <v>46.95</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.9358974227787</v>
+        <v>56.93505623999775</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>36.74494924618723</v>
+        <v>30.82200489805924</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3094505900898822</v>
+        <v>3.649202276918144</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.3180689688000013</v>
+        <v>0.0787766015329823</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6164</v>
+        <v>6174</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>552.1201677836129</v>
+        <v>593.3012113274491</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>13.55</v>
+        <v>48.95</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>58.5123664845092</v>
+        <v>54.93589743242257</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>21.01494992718916</v>
+        <v>36.74494926467982</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.92616437492029</v>
+        <v>0.3094505900898822</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.08741855819453789</v>
+        <v>-0.3180689688103051</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6470</v>
+        <v>6206</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>535.5718533385293</v>
+        <v>592.5525204578106</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>49.8</v>
+        <v>132</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>56.44585056579357</v>
+        <v>50.18461892612314</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.77833580651211</v>
+        <v>20.03605120901469</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9885314736166148</v>
+        <v>0.4426718174121425</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0662449818309986</v>
+        <v>-1.381061348344515</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6291</v>
+        <v>6278</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>535.1089147333516</v>
+        <v>584.4129615742078</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>543</v>
+        <v>204</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.09027021643196</v>
+        <v>50.26824325972294</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>20.92810862054396</v>
+        <v>22.04796999824151</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9602886048741868</v>
+        <v>0.6027078778357343</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-7.02612245651807</v>
+        <v>-2.333649337531036</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6282</v>
+        <v>6291</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>531.481235438902</v>
+        <v>575.1089147333516</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>61.5</v>
+        <v>543</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.53359775782285</v>
+        <v>50.09027022546489</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.83310865014672</v>
+        <v>20.92810866841704</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9585313499581424</v>
+        <v>0.9602886048741868</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.3760736385622996</v>
+        <v>-7.026122457136225</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6285</v>
+        <v>6164</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>526.4772642447116</v>
+        <v>572.1201677836129</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>254</v>
+        <v>13.55</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>40.79291947736084</v>
+        <v>58.51236649114365</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.54580987833303</v>
+        <v>21.01495000050964</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9693734261374296</v>
+        <v>2.92616437492029</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-5.289088317359531</v>
+        <v>0.08741855819453789</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6237</v>
+        <v>6405</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>522.3106515715584</v>
+        <v>570.2976899740869</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>46.3</v>
+        <v>67.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.93378733733316</v>
+        <v>51.48622992136259</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>22.09068873789621</v>
+        <v>32.08775225057876</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.3586296737465923</v>
+        <v>0.9040967109606172</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.4618459436771915</v>
+        <v>-1.553125780573542</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6233</v>
+        <v>6237</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>500.8980402930753</v>
+        <v>562.3106515715584</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>25.45</v>
+        <v>46.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.33280006179563</v>
+        <v>48.93378740035646</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.54342099493594</v>
+        <v>22.09068865773717</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.538592441815885</v>
+        <v>0.3586296737465923</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2250244937293017</v>
+        <v>-0.461845943842041</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6451</v>
+        <v>6224</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>499.3077269766471</v>
+        <v>546.3613328750757</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>596</v>
+        <v>78.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>54.59197434868078</v>
+        <v>49.82917565828345</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32.57181936746783</v>
+        <v>25.10554681906222</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.348472644230178</v>
+        <v>0.4341864315230613</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-5.917034067603971</v>
+        <v>-0.7565261086865873</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6283</v>
+        <v>6284</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>491.8082457822017</v>
+        <v>530.5976164891624</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>24.35</v>
+        <v>101</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>51.85625622408875</v>
+        <v>50.10621401265231</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.54046753559616</v>
+        <v>41.70986031418184</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7795265633449789</v>
+        <v>0.4186394991199239</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0834785209476685</v>
+        <v>-1.093514143836032</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6206</v>
+        <v>6285</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>482.5525204578105</v>
+        <v>526.4772642447116</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>50.18461886005191</v>
+        <v>40.79291949373849</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.03605114779349</v>
+        <v>21.54580987833303</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4426718174121425</v>
+        <v>0.9693734261374296</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.381061348035403</v>
+        <v>-5.289088317565555</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6177</v>
+        <v>6227</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>482.0431989309582</v>
+        <v>520.5701153224047</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>45.9</v>
+        <v>119.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>50.00460586197532</v>
+        <v>47.01629718231957</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.80402459802134</v>
+        <v>22.27504628348726</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5415423051368891</v>
+        <v>0.3535809117091529</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2106187196010749</v>
+        <v>-2.157561482908855</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6227</v>
+        <v>6190</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>480.5701153224047</v>
+        <v>509.6964166980428</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>119.5</v>
+        <v>81.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.0162971110888</v>
+        <v>53.79094351328626</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.27504622800827</v>
+        <v>25.90382610156651</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3535809117091529</v>
+        <v>0.6031973784630207</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-2.157561482146443</v>
+        <v>-0.3712835786951811</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6190</v>
+        <v>6470</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>469.6964166980428</v>
+        <v>505.5718533385288</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>81.7</v>
+        <v>49.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>53.79094348232569</v>
+        <v>56.44585073274361</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>25.90382611855987</v>
+        <v>15.77833584403818</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6031973784630207</v>
+        <v>0.9885314736166148</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.3712835785818382</v>
+        <v>0.0662449816661458</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6278</v>
+        <v>6279</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>459.4129615742078</v>
+        <v>496.3343968368943</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>204</v>
+        <v>120</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.26824326376605</v>
+        <v>52.52891393379767</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>22.04796994179894</v>
+        <v>19.52734670024852</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6027078778357343</v>
+        <v>0.4948297385417176</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.333649337840119</v>
+        <v>-0.2829893470079174</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6279</v>
+        <v>6474</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>456.3343968368943</v>
+        <v>488.9014355179737</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>120</v>
+        <v>37.6</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>52.52891371870742</v>
+        <v>51.40824926061109</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>19.52734670024852</v>
+        <v>17.98952311678072</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4948297385417176</v>
+        <v>2.724738408636555</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.2829893458745933</v>
+        <v>0.3589780977037733</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, market_above_ma60, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6290</v>
+        <v>6234</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>447.6742941652556</v>
+        <v>485.0150170720351</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>306</v>
+        <v>45.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>49.2465529097371</v>
+        <v>49.36334491265167</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15.53781451770665</v>
+        <v>16.46383841062808</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.701333642287151</v>
+        <v>0.5541499434133039</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-4.105824031065341</v>
+        <v>-0.130565782702011</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6263</v>
+        <v>6177</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>438.6358537446088</v>
+        <v>482.0431989309582</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>158</v>
+        <v>45.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.700693027368</v>
+        <v>50.00460603301217</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>16.80724217119508</v>
+        <v>22.80402462164717</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6507183600957682</v>
+        <v>0.5415423051368891</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.666213670173681</v>
+        <v>0.2106187195083518</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6205</v>
+        <v>6283</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>438.414890939954</v>
+        <v>481.8082457822017</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>81.5</v>
+        <v>24.35</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>50.08468905160135</v>
+        <v>51.85625631201792</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.66894088359039</v>
+        <v>16.5404675499687</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5467668311063965</v>
+        <v>0.7795265633449789</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.2508742910357974</v>
+        <v>-0.0834785209476685</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6464</v>
+        <v>6185</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>432.1030571380117</v>
+        <v>470.2349688132208</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>78</v>
+        <v>14.4</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>60.85130971854257</v>
+        <v>54.54724712679436</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.34765091273575</v>
+        <v>16.14923967912017</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3102444127425453</v>
+        <v>0.9124509206972212</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0596276924443473</v>
+        <v>0.0284172965290678</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6405</v>
+        <v>6290</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>430.2976899740869</v>
+        <v>467.6742941652556</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>67.8</v>
+        <v>306</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.48622989534191</v>
+        <v>49.24655293432787</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>32.0877522617355</v>
+        <v>15.5378145044376</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.9040967109606172</v>
+        <v>0.701333642287151</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.553125780501436</v>
+        <v>-4.105824031147778</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6185</v>
+        <v>6263</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>430.2349688132207</v>
+        <v>458.6358537446088</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>14.4</v>
+        <v>158</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.54724682534325</v>
+        <v>44.70069315020055</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.14923966298818</v>
+        <v>16.80724216123479</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9124509206972212</v>
+        <v>0.6507183600957682</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.028417296590886</v>
+        <v>-1.666213670173681</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6214</v>
+        <v>6464</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>428.2092530412394</v>
+        <v>452.1030571380116</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>41.30838580372728</v>
+        <v>60.85130966849725</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.03690375684399</v>
+        <v>14.34765095838903</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.414045108817888</v>
+        <v>0.3102444127425453</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-1.787930913785202</v>
+        <v>-0.0596276924237445</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6198</v>
+        <v>6244</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>407.293485001933</v>
+        <v>435.810112844759</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.6</v>
+        <v>27.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.13539186344173</v>
+        <v>43.52272779479818</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.00594362599618</v>
+        <v>19.38950809526588</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.322678408371567</v>
+        <v>0.3829498539464281</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.4053996735102582</v>
+        <v>-0.2798025283004413</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6244</v>
+        <v>6214</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>395.8101128447591</v>
+        <v>428.2092530412394</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>27.6</v>
+        <v>130</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.5227277473967</v>
+        <v>41.30838590709562</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.38950812756915</v>
+        <v>20.03690376596938</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3829498539464281</v>
+        <v>1.414045108817888</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2798025281562027</v>
+        <v>-1.787930915021553</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6170</v>
+        <v>6205</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>389.4836810294939</v>
+        <v>423.414890939954</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>52.1</v>
+        <v>81.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>52.20443569286384</v>
+        <v>50.08468910420915</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.82927337132611</v>
+        <v>13.66894092027568</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7937199178034302</v>
+        <v>0.5467668311063965</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0041173106909134</v>
+        <v>-0.2508742913036847</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6412</v>
+        <v>6277</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>384.9384673110925</v>
+        <v>406.1363750154098</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>94</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.49360003171349</v>
+        <v>38.85640461180057</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.6812488802785</v>
+        <v>31.58530515541852</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5913565511422593</v>
+        <v>0.6526233385338853</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.7176883223457915</v>
+        <v>-0.8036815172202908</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6438</v>
+        <v>6170</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>357.0514665583057</v>
+        <v>389.4836810294939</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>153.5</v>
+        <v>52.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.75109094976712</v>
+        <v>52.20443586048378</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24.75551518957763</v>
+        <v>15.82927339304512</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8477179762667605</v>
+        <v>0.7937199178034302</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.6118004201110576</v>
+        <v>-0.0041173107733433</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6225</v>
+        <v>6412</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>355.0587531758564</v>
+        <v>384.9384673110925</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>22.55</v>
+        <v>94</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>43.95586658066092</v>
+        <v>50.49360009802957</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12.34950231726008</v>
+        <v>20.6812488861545</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6440500679892612</v>
+        <v>0.5913565511422593</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.2425810632733863</v>
+        <v>-0.7176883224488145</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6191</v>
+        <v>6228</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>342.1223516454322</v>
+        <v>381.9688520271044</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>19.45</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.37241243728542</v>
+        <v>43.62477447261523</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.18305066571182</v>
+        <v>4.330510974137006</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.007991804300938</v>
+        <v>1.838965316494202</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.5948303535525852</v>
+        <v>-0.1327262034243387</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6228</v>
+        <v>6198</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>341.9688520270901</v>
+        <v>377.2934850019332</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>19.45</v>
+        <v>20.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>43.62477404054842</v>
+        <v>51.13539187929916</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4.330510966930257</v>
+        <v>8.005943435573601</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.838965316494202</v>
+        <v>1.322678408371567</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.132726202909193</v>
+        <v>0.405399673427831</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6222</v>
+        <v>6438</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>334.7523171885032</v>
+        <v>357.0514665583056</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>20.75</v>
+        <v>153.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>50.26309064996628</v>
+        <v>43.75109110985956</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25.5859345168058</v>
+        <v>24.75551520251774</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.313472869580512</v>
+        <v>0.8477179762667605</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0448158494563379</v>
+        <v>0.6118004192868289</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6442</v>
+        <v>6225</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>331.4831675302717</v>
+        <v>355.0587531758565</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>1980</v>
+        <v>22.55</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.15894560926901</v>
+        <v>43.95586661749237</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11.56157013192085</v>
+        <v>12.34950239615716</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.40951271080376</v>
+        <v>0.6440500679892612</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>6.998113102688073</v>
+        <v>-0.2425810633764149</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6456</v>
+        <v>6417</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>330.0728058631265</v>
+        <v>350.5425390898222</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>71.7</v>
+        <v>129.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>46.55878821313009</v>
+        <v>45.99446960353843</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.33373223765486</v>
+        <v>16.86925568187727</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3762371785613136</v>
+        <v>0.3522824686849944</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.7237218629172754</v>
+        <v>-1.454411932312977</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6246</v>
+        <v>6192</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>323.3337618110201</v>
+        <v>347.4894757907988</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>15.25</v>
+        <v>120.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.96086328551944</v>
+        <v>45.1417055541659</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.93797644745312</v>
+        <v>25.18381347448441</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.321355717217598</v>
+        <v>0.8366428940414032</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0076257456464331</v>
+        <v>-0.8821718803035232</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6426</v>
+        <v>6442</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>316.5846393620941</v>
+        <v>331.4831675302716</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>217</v>
+        <v>1980</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.58730850236665</v>
+        <v>51.15894562228958</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>19.32398038671328</v>
+        <v>11.56157011975442</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7290744867951553</v>
+        <v>1.40951271080376</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-2.025472562698616</v>
+        <v>6.998113101245513</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4873,21 +4873,21 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6417</v>
+        <v>6456</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>310.5425390898222</v>
+        <v>330.0728058631265</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>129.5</v>
+        <v>71.7</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.99446953845675</v>
+        <v>46.55878821529281</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16.86925566244981</v>
+        <v>12.33373221978705</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3522824686849944</v>
+        <v>0.3762371785613136</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,11 +4916,11 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.454411932251161</v>
+        <v>-0.7237218629893948</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>309.3935758922501</v>
+        <v>329.3935758922501</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>97.2</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.7268753490674</v>
+        <v>42.72687536194976</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.4389390558118</v>
+        <v>22.43893906602564</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.4570846316958781</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-1.000297970273862</v>
+        <v>-1.00029797037689</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6234</v>
+        <v>6426</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>305.0150170720351</v>
+        <v>316.5846393620941</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>45.9</v>
+        <v>217</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.36334490963849</v>
+        <v>46.58730851507936</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.46383840017953</v>
+        <v>19.32398044504505</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5541499434133039</v>
+        <v>0.7290744867951553</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1305657826917058</v>
+        <v>-2.025472563048908</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6277</v>
+        <v>6418</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>296.1363750154098</v>
+        <v>311.5219177399353</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>30.85</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>38.8564045994593</v>
+        <v>45.95457143793937</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>31.58530510899879</v>
+        <v>24.8017549608244</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6526233385338853</v>
+        <v>0.7135222920850205</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.8036815170966595</v>
+        <v>-0.0611368375407547</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6276</v>
+        <v>6191</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>283.1404199010148</v>
+        <v>307.1223516454328</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>23</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>28.17537668368081</v>
+        <v>51.3724124777082</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23.06317552137761</v>
+        <v>17.18305064745974</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>3.168941120337763</v>
+        <v>1.007991804300938</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.1490354661680994</v>
+        <v>0.594830353367122</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6416</v>
+        <v>6222</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>282.8024363182809</v>
+        <v>304.7523171885032</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>20.75</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>41.41814539676135</v>
+        <v>50.26309107746022</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.55991087394564</v>
+        <v>25.58593483341833</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6146004409230272</v>
+        <v>1.313472869580512</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.5388992171484811</v>
+        <v>0.0448158492296728</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6418</v>
+        <v>6230</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>271.5219177399353</v>
+        <v>303.3657520533617</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>30.85</v>
+        <v>133</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.95457141468294</v>
+        <v>43.52967402219623</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>24.8017549608244</v>
+        <v>11.72960770124239</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7135222920850205</v>
+        <v>0.7068477174275242</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0611368374892412</v>
+        <v>0.259332807737878</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6215</v>
+        <v>6246</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>271.3429497671568</v>
+        <v>293.3337618110202</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>106</v>
+        <v>15.25</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>39.78086152358851</v>
+        <v>44.96086337124593</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>19.43319150989997</v>
+        <v>17.9379763871486</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4200571158405623</v>
+        <v>0.321355717217598</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.190767228888814</v>
+        <v>-0.0076257456361306</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6441</v>
+        <v>6423</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>263.0455367051653</v>
+        <v>292.8065369267856</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>22.4</v>
+        <v>81.7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>42.94411050156541</v>
+        <v>36.34939558522065</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.70155938384206</v>
+        <v>27.1112766551257</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4734666414146862</v>
+        <v>0.4708758224964073</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.130662465631414</v>
+        <v>-0.025103203017406</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6167</v>
+        <v>6245</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>259.1571057911108</v>
+        <v>283.9733549299272</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>12.15</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.73639175843308</v>
+        <v>41.98799729258917</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.26663840358573</v>
+        <v>17.74944217077391</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.142027017491758</v>
+        <v>0.5693384083669205</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.07176872552337731</v>
+        <v>-0.8379662949863208</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6272</v>
+        <v>6416</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>255.9952040390008</v>
+        <v>282.802436318281</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>32.15</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>40.07865364496183</v>
+        <v>41.41814558775107</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>26.37807777826389</v>
+        <v>22.55991094436292</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.039917717369461</v>
+        <v>0.6146004409230272</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.6289144744436407</v>
+        <v>-0.5388992176842329</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6423</v>
+        <v>6210</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>252.8065369267856</v>
+        <v>279.9307141426009</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>81.7</v>
+        <v>20.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.34939553595635</v>
+        <v>46.66834118101405</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>27.11127660477671</v>
+        <v>18.34317690406239</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4708758224964073</v>
+        <v>0.1060081846414633</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0251032026259006</v>
+        <v>-0.0751715159665389</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6474</v>
+        <v>6167</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>248.9014355179736</v>
+        <v>279.1571057911111</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>37.6</v>
+        <v>12.15</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>51.40824924953945</v>
+        <v>52.73639187517441</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.9895231143812</v>
+        <v>12.26663849837341</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.724738408636555</v>
+        <v>1.142027017491758</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.3589780977655936</v>
+        <v>0.0717687254527479</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6245</v>
+        <v>6215</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>243.9733549299272</v>
+        <v>271.3429497671566</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>80.59999999999999</v>
+        <v>106</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.98799723319514</v>
+        <v>39.7808613451996</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>17.74944212155456</v>
+        <v>19.43319144612186</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5693384083669205</v>
+        <v>0.4200571158405623</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.8379662947184399</v>
+        <v>-1.190767227096107</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6203</v>
+        <v>6272</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>241.6938792278471</v>
+        <v>255.9952040390007</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>68</v>
+        <v>32.15</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.96458294971801</v>
+        <v>40.07865369289949</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>21.23021616067432</v>
+        <v>26.37807781167737</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.9335999018945224</v>
+        <v>1.039917717369461</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2839991183093694</v>
+        <v>-0.6289144747939394</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6210</v>
+        <v>6176</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>239.930714142601</v>
+        <v>253.6290220456672</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>20.6</v>
+        <v>90</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.66834115214157</v>
+        <v>38.29712672604608</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>18.34317689359581</v>
+        <v>27.15079369435703</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1060081846414633</v>
+        <v>0.8179668063649282</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.07517151595623529</v>
+        <v>-0.7172514118860307</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6183</v>
+        <v>6276</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>238.933918809962</v>
+        <v>253.140419901014</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>90.5</v>
+        <v>23</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>48.78155070685483</v>
+        <v>28.17537727270917</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.55006411826908</v>
+        <v>23.06317572484277</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.64907672225261</v>
+        <v>3.168941120337763</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1485793791494657</v>
+        <v>-0.1490354665183986</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6216</v>
+        <v>6183</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>238.691683453994</v>
+        <v>238.933918809962</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>22.8</v>
+        <v>90.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>46.07041208063141</v>
+        <v>48.78155091777504</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.00939675261911</v>
+        <v>15.55006425381816</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.913662424270692</v>
+        <v>0.64907672225261</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0721327973714176</v>
+        <v>0.1485793789846092</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6192</v>
+        <v>6216</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>237.4894757907988</v>
+        <v>238.691683453994</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>120.5</v>
+        <v>22.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.14170555128808</v>
+        <v>46.0704120502639</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>25.18381349526281</v>
+        <v>17.0093969452383</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.8366428940414032</v>
+        <v>0.913662424270692</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.8821718805095937</v>
+        <v>0.0721327973920227</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6176</v>
+        <v>6441</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>223.6290220456672</v>
+        <v>233.0455367051653</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>90</v>
+        <v>22.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>38.29712669156515</v>
+        <v>42.94411052266777</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>27.1507937208656</v>
+        <v>10.70155944736766</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.8179668063649282</v>
+        <v>0.4734666414146862</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,11 +5923,11 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.7172514115769513</v>
+        <v>-0.1306624651059678</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>41.72454572590808</v>
+        <v>41.72454549391296</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.6077992156211</v>
+        <v>17.60779927560383</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.6175445662531255</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.1378253372297024</v>
+        <v>-0.1378253369412217</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.37112771654168</v>
+        <v>42.37112774611734</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.28711955231902</v>
+        <v>17.28711963207286</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.4194832997711329</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2988080427190465</v>
+        <v>-0.2988080428220738</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6485</v>
+        <v>6203</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>211.4145599886914</v>
+        <v>211.6938792278471</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>42.44545763368859</v>
+        <v>45.96458301375446</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.9891149005205</v>
+        <v>21.23021618426753</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3133327596395242</v>
+        <v>0.9335999018945224</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,48 +6082,48 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-2.096927673343218</v>
+        <v>-0.2839991183917867</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6287</v>
+        <v>6485</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>201.6336657121454</v>
+        <v>211.4145599886915</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G107" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>51.71399387501272</v>
+        <v>42.44545763034783</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>0.9322078587835469</v>
+        <v>18.9891148879937</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.3133327596395242</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,48 +6135,48 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0153085825903483</v>
+        <v>-2.096927673363824</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6266</v>
+        <v>6287</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>198.6157233184616</v>
+        <v>201.4669994133625</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25.7</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G108" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.93502102961779</v>
+        <v>51.71399387501272</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>22.73679057149456</v>
+        <v>0.9229390487499936</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4122606201465665</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1418138518465242</v>
+        <v>-0.0153085825903483</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6194</v>
+        <v>6266</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>198.2499098448514</v>
+        <v>198.6157233184616</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>31.95</v>
+        <v>25.7</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.42634446758198</v>
+        <v>36.93502111281949</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16.90249737539376</v>
+        <v>22.73679064344622</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7503785576695269</v>
+        <v>0.4122606201465665</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.1624833219528192</v>
+        <v>-0.1418138519186444</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6230</v>
+        <v>6477</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>193.3657520533617</v>
+        <v>192.7985887501305</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>133</v>
+        <v>31.55</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>43.52967386575141</v>
+        <v>40.85241866425015</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>11.7296076309051</v>
+        <v>12.82456354907814</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7068477174275242</v>
+        <v>0.7584161283607974</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.259332808768189</v>
+        <v>-0.1390077366757793</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6477</v>
+        <v>6194</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>192.7985887501352</v>
+        <v>168.2499098448515</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>31.55</v>
+        <v>31.95</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.85241852890275</v>
+        <v>38.42634460054242</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.82456351636117</v>
+        <v>16.90249738769936</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7584161283607974</v>
+        <v>0.7503785576695269</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1390077364800218</v>
+        <v>-0.1624833219631182</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6188</v>
+        <v>6235</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>178.5762435921874</v>
+        <v>159.0660845764268</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>77.7</v>
+        <v>40.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.85694549720666</v>
+        <v>42.62242448954628</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.51409461767335</v>
+        <v>15.19092962733468</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.9639281675033752</v>
+        <v>0.5414588687367902</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.3471005751511553</v>
+        <v>-0.1467559977519652</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6235</v>
+        <v>6188</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>159.0660845764268</v>
+        <v>148.5762435921869</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>40.4</v>
+        <v>77.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.62242450189243</v>
+        <v>38.85694555193973</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.19092961036435</v>
+        <v>13.5140945530171</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5414588687367902</v>
+        <v>0.9639281675033752</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1467559977828716</v>
+        <v>-0.347100575419043</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6491,13 +6491,13 @@
         <v>53.34169316108114</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.86867626400652</v>
+        <v>16.868676324851</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.8318558343861261</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1638216079929745</v>
+        <v>0.1638216081166102</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>129.6893771603094</v>
+        <v>129.6893771603095</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.02625868147452</v>
+        <v>48.0262578347586</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>7.547863907722176</v>
+        <v>7.547865244337134</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.3848192002148025</v>
+        <v>-0.3848191946718416</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.46884748372894</v>
+        <v>46.46884765163502</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>12.33085536336934</v>
